--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTuanNB_140726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTuanNB_140726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216F8DE4-8E39-42C8-A9B7-16729EB7A245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B9407E-C077-41F3-9E82-A4602CA4291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>0032003E43</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>VNSH02</t>
+  </si>
+  <si>
+    <t>VNSH01</t>
   </si>
 </sst>
 </file>
@@ -414,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -484,6 +493,114 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -502,113 +619,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,14 +643,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>269800</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>247819</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>161190</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>1223596</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>51287</xdr:rowOff>
     </xdr:to>
@@ -669,7 +681,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="269800" y="161190"/>
+          <a:off x="606838" y="161190"/>
           <a:ext cx="1833027" cy="527539"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -969,513 +981,546 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z44"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="12.5703125" style="3" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="1"/>
-    <col min="12" max="13" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="24" width="9.140625" style="1"/>
-    <col min="25" max="25" width="14" style="1" customWidth="1"/>
-    <col min="26" max="26" width="19.28515625" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="12.5703125" style="3" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="13" max="14" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14" style="1" customWidth="1"/>
+    <col min="27" max="27" width="19.28515625" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="31"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="59" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="35"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="50" t="s">
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="35"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="52"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="53" t="s">
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="35"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="55"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="56" t="s">
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="58"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="64"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="10"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="17"/>
       <c r="H6" s="10"/>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="10"/>
+      <c r="J6" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="10"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="17"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="Z8" s="2"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="G8" s="30"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="AA8" s="2"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="Z9" s="2"/>
-    </row>
-    <row r="10" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="AA9" s="2"/>
+    </row>
+    <row r="10" spans="1:27" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="E10" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="F10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="G10" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="I10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="45" t="s">
+      <c r="J10" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="Z10" s="2"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+      <c r="AA10" s="2"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
         <v>1</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="D11" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="E11" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="F11" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="34" t="s">
+      <c r="G11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="34">
+      <c r="H11" s="25">
         <v>1</v>
       </c>
-      <c r="H11" s="37">
+      <c r="I11" s="28">
         <v>260000</v>
       </c>
-      <c r="I11" s="37">
-        <f>SUM(G11*H11)</f>
+      <c r="J11" s="28">
+        <f>SUM(H11*I11)</f>
         <v>260000</v>
       </c>
-      <c r="Z11" s="2"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="38">
+      <c r="AA11" s="2"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="33">
         <v>2</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="D12" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="65" t="s">
+      <c r="E12" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="F12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="G12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="34">
+      <c r="H12" s="25">
         <v>1</v>
       </c>
-      <c r="H12" s="37">
+      <c r="I12" s="28">
         <v>150000</v>
       </c>
-      <c r="I12" s="37">
-        <f t="shared" ref="I12:I13" si="0">SUM(G12*H12)</f>
+      <c r="J12" s="28">
+        <f t="shared" ref="J12:J13" si="0">SUM(H12*I12)</f>
         <v>150000</v>
       </c>
-      <c r="Z12" s="2"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="34" t="s">
+      <c r="AA12" s="2"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="G13" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="34">
+      <c r="H13" s="25">
         <v>2</v>
       </c>
-      <c r="H13" s="37">
+      <c r="I13" s="28">
         <v>100000</v>
       </c>
-      <c r="I13" s="37">
+      <c r="J13" s="28">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
-      <c r="Z13" s="2"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="AA13" s="2"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="24">
-        <f>SUM(I11:I13)</f>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="24">
+        <f>SUM(J11:J13)</f>
         <v>610000</v>
       </c>
-      <c r="Z14" s="2"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA14" s="2"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
-      <c r="I15" s="12"/>
-      <c r="Z15" s="2"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="AA15" s="2"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="14"/>
+      <c r="E16" s="5"/>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
-      <c r="I16" s="20"/>
-      <c r="Z16" s="2"/>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="I16" s="14"/>
+      <c r="J16" s="20"/>
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="29" t="s">
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="Z17" s="2"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="30" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="Z18" s="2"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="66"/>
+      <c r="AA18" s="2"/>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="23"/>
-      <c r="B19" s="21"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
       <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="22"/>
       <c r="H19" s="21"/>
       <c r="I19" s="21"/>
-      <c r="Z19" s="2"/>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J19" s="21"/>
+      <c r="AA19" s="2"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
-      <c r="B20" s="21"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="21"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21"/>
-      <c r="Z20" s="2"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J20" s="21"/>
+      <c r="AA20" s="2"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
-      <c r="B21" s="7"/>
+      <c r="B21" s="19"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="7"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="Z21" s="2"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J21" s="7"/>
+      <c r="AA21" s="2"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="19"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="19"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="Z22" s="2"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="J22" s="7"/>
+      <c r="AA22" s="2"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="19"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="19"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
-      <c r="Z23" s="2"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="J23" s="7"/>
+      <c r="AA23" s="2"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="28" t="s">
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="13"/>
-      <c r="Z24" s="2"/>
-    </row>
-    <row r="25" spans="1:26" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="13"/>
+      <c r="AA24" s="2"/>
+    </row>
+    <row r="25" spans="1:27" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
-      <c r="Z25" s="2"/>
-    </row>
-    <row r="26" spans="1:26" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E26" s="4"/>
-      <c r="Z26" s="2"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z27" s="2"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z28" s="2"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z29" s="2"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z30" s="2"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z31" s="2"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="Z32" s="2"/>
-    </row>
-    <row r="33" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z33" s="2"/>
-    </row>
-    <row r="34" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z34" s="2"/>
-    </row>
-    <row r="35" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z35" s="2"/>
-    </row>
-    <row r="36" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z36" s="2"/>
-    </row>
-    <row r="37" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z37" s="2"/>
-    </row>
-    <row r="38" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z38" s="2"/>
-    </row>
-    <row r="39" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z39" s="2"/>
-    </row>
-    <row r="40" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z40" s="2"/>
-    </row>
-    <row r="41" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z41" s="2"/>
-    </row>
-    <row r="42" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z42" s="2"/>
-    </row>
-    <row r="43" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z43" s="2"/>
-    </row>
-    <row r="44" spans="26:26" x14ac:dyDescent="0.25">
-      <c r="Z44" s="2"/>
+      <c r="J25" s="6"/>
+      <c r="AA25" s="2"/>
+    </row>
+    <row r="26" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F26" s="4"/>
+      <c r="AA26" s="2"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA27" s="2"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA28" s="2"/>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA29" s="2"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA30" s="2"/>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA31" s="2"/>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AA32" s="2"/>
+    </row>
+    <row r="33" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA33" s="2"/>
+    </row>
+    <row r="34" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA34" s="2"/>
+    </row>
+    <row r="35" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA35" s="2"/>
+    </row>
+    <row r="36" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA36" s="2"/>
+    </row>
+    <row r="37" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA37" s="2"/>
+    </row>
+    <row r="38" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA38" s="2"/>
+    </row>
+    <row r="39" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA39" s="2"/>
+    </row>
+    <row r="40" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA40" s="2"/>
+    </row>
+    <row r="41" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA41" s="2"/>
+    </row>
+    <row r="42" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA42" s="2"/>
+    </row>
+    <row r="43" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA43" s="2"/>
+    </row>
+    <row r="44" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA44" s="2"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A1:D4"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="E3:J3"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="F24:I24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0" top="1.75" bottom="0" header="0" footer="0"/>
   <pageSetup scale="28" orientation="landscape" r:id="rId2"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTuanNB_140726.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_AnhTuanNB_140726.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B9407E-C077-41F3-9E82-A4602CA4291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E09F0D-DF6F-4A77-9ACE-314C4AA26C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>VNSH01</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Khách hàng đã đồng ý sửa chữa công nợ ghi KD Lực</t>
   </si>
 </sst>
 </file>
@@ -517,6 +523,24 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -601,27 +625,7 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1003,82 +1007,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="35"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="41" t="s">
+      <c r="A1" s="41"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="44" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="35"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="47" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="50" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="52"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="63"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="17"/>
@@ -1089,11 +1093,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1103,11 +1107,11 @@
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="29"/>
       <c r="E8" s="29"/>
       <c r="F8" s="29" t="s">
@@ -1120,11 +1124,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="65"/>
       <c r="D9" s="29"/>
       <c r="E9" s="29"/>
       <c r="F9" s="29"/>
@@ -1165,6 +1169,9 @@
       <c r="J10" s="31" t="s">
         <v>19</v>
       </c>
+      <c r="K10" s="67" t="s">
+        <v>37</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1199,22 +1206,25 @@
         <f>SUM(H11*I11)</f>
         <v>260000</v>
       </c>
+      <c r="K11" s="67" t="s">
+        <v>38</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="33">
+      <c r="A12" s="39">
         <v>2</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="59" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="27" t="s">
@@ -1236,11 +1246,11 @@
       <c r="AA12" s="2"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="54"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="60"/>
       <c r="F13" s="25" t="s">
         <v>31</v>
       </c>
@@ -1260,17 +1270,17 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="63"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="35"/>
       <c r="J14" s="24">
         <f>SUM(J11:J13)</f>
         <v>610000</v>
@@ -1304,37 +1314,37 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
       <c r="E17" s="8"/>
       <c r="F17" s="16"/>
-      <c r="G17" s="65" t="s">
+      <c r="G17" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="65"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
       <c r="E18" s="10"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
@@ -1405,20 +1415,20 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
       <c r="E24" s="9"/>
       <c r="F24" s="13"/>
-      <c r="G24" s="64" t="s">
+      <c r="G24" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
       <c r="K24" s="13"/>
       <c r="AA24" s="2"/>
     </row>
@@ -1496,13 +1506,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="22">
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="G17:J17"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G24:J24"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="D12:D13"/>
@@ -1518,6 +1521,13 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G24:J24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
